--- a/output_data/charts/0500000US39083.xlsx
+++ b/output_data/charts/0500000US39083.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.6024195000572954</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.6217966226963801</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.605066636944095</c:v>
+                  <c:v>0.6003949547713084</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5931918839838192</c:v>
+                  <c:v>0.5884328179216169</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5744034432559023</c:v>
+                  <c:v>0.5887380115848447</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6174984207201516</c:v>
+                  <c:v>0.7025132609244759</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.8347951384538279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.8054086794244275</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>0.9672391908610356</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9410378485104214</c:v>
+                  <c:v>0.9412027009810167</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9177685752202484</c:v>
+                  <c:v>0.9162282735573003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.9699981011456421</c:v>
+                  <c:v>0.9733168739910739</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.013897662665824</c:v>
+                  <c:v>1.021406920939631</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.050933466984087</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.22939414277997</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>1.625990134802937</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.902775345126825</c:v>
+                  <c:v>1.907886354949675</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.952256847289065</c:v>
+                  <c:v>1.957178720478421</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.05234508513197</c:v>
+                  <c:v>2.065330927737157</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.100442198357549</c:v>
+                  <c:v>2.123326597625663</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.139456208495176</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2111742269222584</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2667137968155016</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2706877060013057</c:v>
+                  <c:v>0.2707351254936934</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2925986920998354</c:v>
+                  <c:v>0.2926174067381954</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2990695613646434</c:v>
+                  <c:v>0.2975342639192226</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2921667719519899</c:v>
+                  <c:v>0.2873200303106845</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2803533391805538</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.070604220210519</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>1.327142145600026</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.331146601277009</c:v>
+                  <c:v>1.331379793604281</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.418224261707945</c:v>
+                  <c:v>1.416715969235197</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.44471169061333</c:v>
+                  <c:v>1.441775076757509</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.468730259001895</c:v>
+                  <c:v>1.458701692346552</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.487908783360481</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>96.08099923060553</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>95.19111810922412</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>94.94928586214034</c:v>
+                  <c:v>94.94840107020003</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>94.82595973969909</c:v>
+                  <c:v>94.82882681206927</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>94.65947211848851</c:v>
+                  <c:v>94.63330484601019</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>94.50726468730259</c:v>
+                  <c:v>94.40673149785299</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>94.20655306352587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>0.605066636944095</v>
+        <v>0.6003949547713084</v>
       </c>
       <c r="C12" s="2">
-        <v>0.9410378485104214</v>
+        <v>0.9412027009810167</v>
       </c>
       <c r="D12" s="2">
-        <v>1.902775345126825</v>
+        <v>1.907886354949675</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2706877060013057</v>
+        <v>0.2707351254936934</v>
       </c>
       <c r="F12" s="2">
-        <v>1.331146601277009</v>
+        <v>1.331379793604281</v>
       </c>
       <c r="G12" s="2">
-        <v>94.94928586214034</v>
+        <v>94.94840107020003</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>0.5931918839838192</v>
+        <v>0.5884328179216169</v>
       </c>
       <c r="C13" s="2">
-        <v>0.9177685752202484</v>
+        <v>0.9162282735573003</v>
       </c>
       <c r="D13" s="2">
-        <v>1.952256847289065</v>
+        <v>1.957178720478421</v>
       </c>
       <c r="E13" s="2">
-        <v>0.2925986920998354</v>
+        <v>0.2926174067381954</v>
       </c>
       <c r="F13" s="2">
-        <v>1.418224261707945</v>
+        <v>1.416715969235197</v>
       </c>
       <c r="G13" s="2">
-        <v>94.82595973969909</v>
+        <v>94.82882681206927</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>0.5744034432559023</v>
+        <v>0.5887380115848447</v>
       </c>
       <c r="C14" s="2">
-        <v>0.9699981011456421</v>
+        <v>0.9733168739910739</v>
       </c>
       <c r="D14" s="2">
-        <v>2.05234508513197</v>
+        <v>2.065330927737157</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2990695613646434</v>
+        <v>0.2975342639192226</v>
       </c>
       <c r="F14" s="2">
-        <v>1.44471169061333</v>
+        <v>1.441775076757509</v>
       </c>
       <c r="G14" s="2">
-        <v>94.65947211848851</v>
+        <v>94.63330484601019</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>0.6174984207201516</v>
+        <v>0.7025132609244759</v>
       </c>
       <c r="C15" s="2">
-        <v>1.013897662665824</v>
+        <v>1.021406920939631</v>
       </c>
       <c r="D15" s="2">
-        <v>2.100442198357549</v>
+        <v>2.123326597625663</v>
       </c>
       <c r="E15" s="2">
-        <v>0.2921667719519899</v>
+        <v>0.2873200303106845</v>
       </c>
       <c r="F15" s="2">
-        <v>1.468730259001895</v>
+        <v>1.458701692346552</v>
       </c>
       <c r="G15" s="2">
-        <v>94.50726468730259</v>
+        <v>94.40673149785299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.8347951384538279</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1.050933466984087</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.139456208495176</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2803533391805538</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.487908783360481</v>
+      </c>
+      <c r="G16" s="2">
+        <v>94.20655306352587</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39083.xlsx
+++ b/output_data/charts/0500000US39083.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.6024195000572954</c:v>
+                  <c:v>0.6023899165166148</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6510034263338228</c:v>
+                  <c:v>0.6478142388590638</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6416478833846103</c:v>
+                  <c:v>0.6368902639720887</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6685062908577247</c:v>
+                  <c:v>0.6589109073581123</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6225935938396002</c:v>
+                  <c:v>0.6131147540983607</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.611024653943812</c:v>
+                  <c:v>0.6032687988721497</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6037438682263383</c:v>
+                  <c:v>0.5746277233249603</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6585703806341184</c:v>
+                  <c:v>0.6087708703954563</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6427544774793689</c:v>
+                  <c:v>0.6009693053311793</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.6217966226963801</c:v>
+                  <c:v>0.5744359937100864</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.6003949547713084</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.8054086794244275</c:v>
+                  <c:v>0.8037321983958093</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8451623429596998</c:v>
+                  <c:v>0.8468906548308666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8292064954508811</c:v>
+                  <c:v>0.8360213284181424</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.8442561019677408</c:v>
+                  <c:v>0.8593775674521017</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.8634390104038667</c:v>
+                  <c:v>0.8819672131147541</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8862314685887459</c:v>
+                  <c:v>0.9114604678611826</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.9253031023903664</c:v>
+                  <c:v>0.9571656077098623</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.9047192110196431</c:v>
+                  <c:v>0.9351895676584355</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.9431372232360588</c:v>
+                  <c:v>0.9789983844911146</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.9672391908610356</c:v>
+                  <c:v>0.9964378550110715</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.9412027009810167</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.22939414277997</c:v>
+                  <c:v>1.230970698968735</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.318322728014358</c:v>
+                  <c:v>1.318473312337842</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.352396308056794</c:v>
+                  <c:v>1.35112895793562</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.381360664892743</c:v>
+                  <c:v>1.380262249827467</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.397558777750471</c:v>
+                  <c:v>1.39344262295082</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.464493406503399</c:v>
+                  <c:v>1.458992475533188</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.484750545502272</c:v>
+                  <c:v>1.469405178216684</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.516015975222105</c:v>
+                  <c:v>1.491733446491815</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.551977519742898</c:v>
+                  <c:v>1.51373182552504</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.625990134802937</c:v>
+                  <c:v>1.569269278906325</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.907886354949675</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2111742269222584</c:v>
+                  <c:v>0.211163856605009</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2170011421112743</c:v>
+                  <c:v>0.2170259288872934</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2270446356591698</c:v>
+                  <c:v>0.2271081561450859</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2135278078906737</c:v>
+                  <c:v>0.2136120148542509</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2195461620381748</c:v>
+                  <c:v>0.219672131147541</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.22278646899828</c:v>
+                  <c:v>0.222947164800577</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2313257755975916</c:v>
+                  <c:v>0.2314928828251983</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2445187056809846</c:v>
+                  <c:v>0.2448140229472344</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2519339157959335</c:v>
+                  <c:v>0.2536348949919224</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2667137968155016</c:v>
+                  <c:v>0.2663585892622188</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.2707351254936934</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.070604220210519</c:v>
+                  <c:v>1.068914715992797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.114374286180454</c:v>
+                  <c:v>1.10960625295759</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.153320939109261</c:v>
+                  <c:v>1.145415048383912</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.189185637791137</c:v>
+                  <c:v>1.183081928423543</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.232079954124683</c:v>
+                  <c:v>1.232786885245902</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.215496764681792</c:v>
+                  <c:v>1.213094867297257</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.223893819828392</c:v>
+                  <c:v>1.229703327915415</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.247045398973021</c:v>
+                  <c:v>1.2599761714351</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.30488848694304</c:v>
+                  <c:v>1.316639741518578</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.327142145600026</c:v>
+                  <c:v>1.331792946311094</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.331379793604281</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>96.08099923060553</c:v>
+                  <c:v>96.08282861352103</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>95.85413607440039</c:v>
+                  <c:v>95.86018961212734</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>95.79638373833929</c:v>
+                  <c:v>95.80343624514515</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95.70316349659998</c:v>
+                  <c:v>95.70475533208452</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>95.66478250184321</c:v>
+                  <c:v>95.65901639344261</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>95.59996723728396</c:v>
+                  <c:v>95.59023622563565</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>95.53098288845504</c:v>
+                  <c:v>95.53760528000788</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>95.42913032847012</c:v>
+                  <c:v>95.45951592107195</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>95.3053083768027</c:v>
+                  <c:v>95.33602584814217</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>95.19111810922412</c:v>
+                  <c:v>95.26170533679921</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>94.94840107020003</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>0.6024195000572954</v>
+        <v>0.6023899165166148</v>
       </c>
       <c r="C2" s="2">
-        <v>0.8054086794244275</v>
+        <v>0.8037321983958093</v>
       </c>
       <c r="D2" s="2">
-        <v>1.22939414277997</v>
+        <v>1.230970698968735</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2111742269222584</v>
+        <v>0.211163856605009</v>
       </c>
       <c r="F2" s="2">
-        <v>1.070604220210519</v>
+        <v>1.068914715992797</v>
       </c>
       <c r="G2" s="2">
-        <v>96.08099923060553</v>
+        <v>96.08282861352103</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.6510034263338228</v>
+        <v>0.6478142388590638</v>
       </c>
       <c r="C3" s="2">
-        <v>0.8451623429596998</v>
+        <v>0.8468906548308666</v>
       </c>
       <c r="D3" s="2">
-        <v>1.318322728014358</v>
+        <v>1.318473312337842</v>
       </c>
       <c r="E3" s="2">
-        <v>0.2170011421112743</v>
+        <v>0.2170259288872934</v>
       </c>
       <c r="F3" s="2">
-        <v>1.114374286180454</v>
+        <v>1.10960625295759</v>
       </c>
       <c r="G3" s="2">
-        <v>95.85413607440039</v>
+        <v>95.86018961212734</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.6416478833846103</v>
+        <v>0.6368902639720887</v>
       </c>
       <c r="C4" s="2">
-        <v>0.8292064954508811</v>
+        <v>0.8360213284181424</v>
       </c>
       <c r="D4" s="2">
-        <v>1.352396308056794</v>
+        <v>1.35112895793562</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2270446356591698</v>
+        <v>0.2271081561450859</v>
       </c>
       <c r="F4" s="2">
-        <v>1.153320939109261</v>
+        <v>1.145415048383912</v>
       </c>
       <c r="G4" s="2">
-        <v>95.79638373833929</v>
+        <v>95.80343624514515</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.6685062908577247</v>
+        <v>0.6589109073581123</v>
       </c>
       <c r="C5" s="2">
-        <v>0.8442561019677408</v>
+        <v>0.8593775674521017</v>
       </c>
       <c r="D5" s="2">
-        <v>1.381360664892743</v>
+        <v>1.380262249827467</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2135278078906737</v>
+        <v>0.2136120148542509</v>
       </c>
       <c r="F5" s="2">
-        <v>1.189185637791137</v>
+        <v>1.183081928423543</v>
       </c>
       <c r="G5" s="2">
-        <v>95.70316349659998</v>
+        <v>95.70475533208452</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.6225935938396002</v>
+        <v>0.6131147540983607</v>
       </c>
       <c r="C6" s="2">
-        <v>0.8634390104038667</v>
+        <v>0.8819672131147541</v>
       </c>
       <c r="D6" s="2">
-        <v>1.397558777750471</v>
+        <v>1.39344262295082</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2195461620381748</v>
+        <v>0.219672131147541</v>
       </c>
       <c r="F6" s="2">
-        <v>1.232079954124683</v>
+        <v>1.232786885245902</v>
       </c>
       <c r="G6" s="2">
-        <v>95.66478250184321</v>
+        <v>95.65901639344261</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.611024653943812</v>
+        <v>0.6032687988721497</v>
       </c>
       <c r="C7" s="2">
-        <v>0.8862314685887459</v>
+        <v>0.9114604678611826</v>
       </c>
       <c r="D7" s="2">
-        <v>1.464493406503399</v>
+        <v>1.458992475533188</v>
       </c>
       <c r="E7" s="2">
-        <v>0.22278646899828</v>
+        <v>0.222947164800577</v>
       </c>
       <c r="F7" s="2">
-        <v>1.215496764681792</v>
+        <v>1.213094867297257</v>
       </c>
       <c r="G7" s="2">
-        <v>95.59996723728396</v>
+        <v>95.59023622563565</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.6037438682263383</v>
+        <v>0.5746277233249603</v>
       </c>
       <c r="C8" s="2">
-        <v>0.9253031023903664</v>
+        <v>0.9571656077098623</v>
       </c>
       <c r="D8" s="2">
-        <v>1.484750545502272</v>
+        <v>1.469405178216684</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2313257755975916</v>
+        <v>0.2314928828251983</v>
       </c>
       <c r="F8" s="2">
-        <v>1.223893819828392</v>
+        <v>1.229703327915415</v>
       </c>
       <c r="G8" s="2">
-        <v>95.53098288845504</v>
+        <v>95.53760528000788</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.6585703806341184</v>
+        <v>0.6087708703954563</v>
       </c>
       <c r="C9" s="2">
-        <v>0.9047192110196431</v>
+        <v>0.9351895676584355</v>
       </c>
       <c r="D9" s="2">
-        <v>1.516015975222105</v>
+        <v>1.491733446491815</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2445187056809846</v>
+        <v>0.2448140229472344</v>
       </c>
       <c r="F9" s="2">
-        <v>1.247045398973021</v>
+        <v>1.2599761714351</v>
       </c>
       <c r="G9" s="2">
-        <v>95.42913032847012</v>
+        <v>95.45951592107195</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.6427544774793689</v>
+        <v>0.6009693053311793</v>
       </c>
       <c r="C10" s="2">
-        <v>0.9431372232360588</v>
+        <v>0.9789983844911146</v>
       </c>
       <c r="D10" s="2">
-        <v>1.551977519742898</v>
+        <v>1.51373182552504</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2519339157959335</v>
+        <v>0.2536348949919224</v>
       </c>
       <c r="F10" s="2">
-        <v>1.30488848694304</v>
+        <v>1.316639741518578</v>
       </c>
       <c r="G10" s="2">
-        <v>95.3053083768027</v>
+        <v>95.33602584814217</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.6217966226963801</v>
+        <v>0.5744359937100864</v>
       </c>
       <c r="C11" s="2">
-        <v>0.9672391908610356</v>
+        <v>0.9964378550110715</v>
       </c>
       <c r="D11" s="2">
-        <v>1.625990134802937</v>
+        <v>1.569269278906325</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2667137968155016</v>
+        <v>0.2663585892622188</v>
       </c>
       <c r="F11" s="2">
-        <v>1.327142145600026</v>
+        <v>1.331792946311094</v>
       </c>
       <c r="G11" s="2">
-        <v>95.19111810922412</v>
+        <v>95.26170533679921</v>
       </c>
     </row>
     <row r="12" spans="1:7">
